--- a/Collections/EURO/Ireland/#EURO#Ireland#Regular#[2002-present]#circulation_quality.xlsx
+++ b/Collections/EURO/Ireland/#EURO#Ireland#Regular#[2002-present]#circulation_quality.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24332"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24334"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Lord_Alexator\Documents\CoinCollection\Collections\EURO\Ireland\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AED2D4E8-5078-401B-9CE8-088543818544}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C455DC2F-3F0C-4B70-8401-4BFC4410776A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21220" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -46,6 +46,9 @@
         <xcalcf:feature name="microsoft.com:CNMTM"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
       </xcalcf:calcFeatures>
+    </ext>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
     </ext>
   </extLst>
 </workbook>
@@ -471,7 +474,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="763" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="837" uniqueCount="169">
   <si>
     <t>-</t>
   </si>
@@ -965,9 +968,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>60.000</t>
-  </si>
-  <si>
     <t>Subject</t>
   </si>
   <si>
@@ -978,6 +978,9 @@
   </si>
   <si>
     <t>Subtype_2#Special_distinctions_1</t>
+  </si>
+  <si>
+    <t>7.000</t>
   </si>
 </sst>
 </file>
@@ -1276,7 +1279,103 @@
     <cellStyle name="Обычный" xfId="0" builtinId="0"/>
     <cellStyle name="Обычный 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
   </cellStyles>
-  <dxfs count="34">
+  <dxfs count="46">
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor rgb="FF9BE5FF"/>
+          <bgColor rgb="FF9BE5FF"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="1" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
@@ -1565,9 +1664,9 @@
     <filterColumn colId="2" hiddenButton="1"/>
   </autoFilter>
   <tableColumns count="3">
-    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="2"/>
-    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="1" dataCellStyle="Гиперссылка"/>
-    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="0"/>
+    <tableColumn id="1" xr3:uid="{00000000-0010-0000-0000-000001000000}" name="№" dataDxfId="14"/>
+    <tableColumn id="2" xr3:uid="{00000000-0010-0000-0000-000002000000}" name="Link" dataDxfId="13" dataCellStyle="Гиперссылка"/>
+    <tableColumn id="3" xr3:uid="{00000000-0010-0000-0000-000003000000}" name="Description (single table, table set, mintage, prices):" dataDxfId="12"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium9" showFirstColumn="1" showLastColumn="0" showRowStripes="0" showColumnStripes="0"/>
 </table>
@@ -1836,7 +1935,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -1867,13 +1966,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -2359,13 +2458,57 @@
       </c>
       <c r="D24" s="13"/>
       <c r="E24" s="25" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -2377,7 +2520,7 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="33" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="45" priority="5" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
@@ -2392,7 +2535,7 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="32" priority="3" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="44" priority="3" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
@@ -2406,8 +2549,8 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F24">
-    <cfRule type="containsText" dxfId="31" priority="1" operator="containsText" text="*-">
+  <conditionalFormatting sqref="F20:F26">
+    <cfRule type="containsText" dxfId="43" priority="1" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
@@ -2429,7 +2572,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -2460,13 +2603,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -2892,7 +3035,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G24" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G21:G26" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -2958,6 +3101,50 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -2970,11 +3157,26 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="30" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="42" priority="7" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="41" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -2986,9 +3188,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="29" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F20:F24">
+    <cfRule type="containsText" dxfId="40" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -3001,9 +3203,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F24">
-    <cfRule type="containsText" dxfId="28" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F25:F26">
+    <cfRule type="containsText" dxfId="11" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -3024,7 +3226,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3055,13 +3257,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
-        <v>166</v>
-      </c>
       <c r="D2" s="7" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -3509,7 +3711,7 @@
         <v>0</v>
       </c>
       <c r="G22" s="3" t="str">
-        <f t="shared" ref="G22:G24" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G22:G26" si="2">IF(OR(AND(F22&gt;1,F22&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -3553,6 +3755,50 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="13"/>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="13"/>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="2"/>
         <v/>
       </c>
@@ -3564,11 +3810,26 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="27" priority="17" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="39" priority="19" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="20">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="38" priority="17" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="18">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -3580,11 +3841,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="26" priority="15" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="16">
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="37" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3595,9 +3856,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="25" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="36" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
       <colorScale>
@@ -3610,11 +3871,11 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="24" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="10">
+  <conditionalFormatting sqref="F22:F24">
+    <cfRule type="containsText" dxfId="35" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -3625,9 +3886,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22:F24">
-    <cfRule type="containsText" dxfId="23" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+  <conditionalFormatting sqref="F25:F26">
+    <cfRule type="containsText" dxfId="10" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -3648,7 +3909,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -3679,13 +3940,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -4215,13 +4476,61 @@
         <v>9</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
         <f t="shared" si="2"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="3">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="3"/>
         <v/>
       </c>
     </row>
@@ -4233,11 +4542,41 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="22" priority="9" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="34" priority="13" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="14">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="33" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="12">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="32" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="10">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -4249,24 +4588,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="21" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
-    </cfRule>
-    <cfRule type="colorScale" priority="8">
-      <colorScale>
-        <cfvo type="formula" val="0"/>
-        <cfvo type="formula" val="1"/>
-        <cfvo type="formula" val="10"/>
-        <color rgb="FFFF9F9F"/>
-        <color rgb="FFD1E0B2"/>
-        <color rgb="FF00B050"/>
-      </colorScale>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="20" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F21:F24">
+    <cfRule type="containsText" dxfId="31" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -4279,9 +4603,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21:F24">
-    <cfRule type="containsText" dxfId="19" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="9" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="8" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -4302,7 +4641,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4333,13 +4672,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -4869,13 +5208,61 @@
         <v>9</v>
       </c>
       <c r="E24" s="25" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F24" s="1" t="s">
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
         <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" ref="G25:G26" si="2">IF(OR(AND(F25&gt;1,F25&lt;&gt;"-")),"Can exchange","")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
+        <f t="shared" si="2"/>
         <v/>
       </c>
     </row>
@@ -4887,12 +5274,12 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="18" priority="7" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="30" priority="11" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="colorScale" priority="8">
+    <cfRule type="colorScale" priority="12">
       <colorScale>
         <cfvo type="formula" val="0"/>
         <cfvo type="formula" val="1"/>
@@ -4904,8 +5291,23 @@
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="17" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="29" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F24">
+    <cfRule type="containsText" dxfId="28" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -4918,9 +5320,24 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F24">
-    <cfRule type="containsText" dxfId="16" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="4">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -4941,7 +5358,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0500-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -4972,13 +5389,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -5442,7 +5859,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G24" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G21:G26" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -5460,7 +5877,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -5514,6 +5931,54 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -5526,11 +5991,41 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="27" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="26" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F24">
+    <cfRule type="containsText" dxfId="25" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -5542,9 +6037,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="14" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="5" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -5557,9 +6052,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F24">
-    <cfRule type="containsText" dxfId="13" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="4" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -5580,7 +6075,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0600-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -5611,13 +6106,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -6082,7 +6577,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G24" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G21:G26" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6100,7 +6595,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -6154,6 +6649,54 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6165,11 +6708,41 @@
     <mergeCell ref="C1:D1"/>
   </mergeCells>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="12" priority="13" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="24" priority="17" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="18">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="23" priority="15" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="16">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20">
+    <cfRule type="containsText" dxfId="22" priority="13" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="14">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6181,9 +6754,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="11" priority="11" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F21">
+    <cfRule type="containsText" dxfId="21" priority="11" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="12">
       <colorScale>
@@ -6196,9 +6769,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20">
-    <cfRule type="containsText" dxfId="10" priority="9" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F22">
+    <cfRule type="containsText" dxfId="20" priority="9" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="10">
       <colorScale>
@@ -6211,9 +6784,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F21">
-    <cfRule type="containsText" dxfId="9" priority="7" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F21))))</formula>
+  <conditionalFormatting sqref="F23">
+    <cfRule type="containsText" dxfId="19" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="8">
       <colorScale>
@@ -6226,9 +6799,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F22">
-    <cfRule type="containsText" dxfId="8" priority="5" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F22))))</formula>
+  <conditionalFormatting sqref="F24">
+    <cfRule type="containsText" dxfId="18" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
@@ -6241,9 +6814,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F23">
-    <cfRule type="containsText" dxfId="7" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F23))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="3" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6256,9 +6829,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F24">
-    <cfRule type="containsText" dxfId="6" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F24))))</formula>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="2" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
@@ -6279,7 +6852,7 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0700-000000000000}">
-  <dimension ref="A1:I24"/>
+  <dimension ref="A1:I26"/>
   <sheetFormatPr defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="5.6328125" style="4" customWidth="1"/>
@@ -6310,13 +6883,13 @@
     <row r="2" spans="1:9" ht="15" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A2" s="29"/>
       <c r="B2" s="27" t="s">
+        <v>164</v>
+      </c>
+      <c r="C2" s="7" t="s">
         <v>165</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="D2" s="7" t="s">
         <v>166</v>
-      </c>
-      <c r="D2" s="7" t="s">
-        <v>167</v>
       </c>
       <c r="E2" s="9" t="s">
         <v>28</v>
@@ -6781,7 +7354,7 @@
         <v>0</v>
       </c>
       <c r="G21" s="3" t="str">
-        <f t="shared" ref="G21:G24" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
+        <f t="shared" ref="G21:G26" si="1">IF(OR(AND(F21&gt;1,F21&lt;&gt;"-")),"Can exchange","")</f>
         <v/>
       </c>
     </row>
@@ -6799,7 +7372,7 @@
         <v>9</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>161</v>
+        <v>168</v>
       </c>
       <c r="F22" s="1" t="s">
         <v>0</v>
@@ -6853,6 +7426,54 @@
         <v>0</v>
       </c>
       <c r="G24" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="10">
+        <v>2024</v>
+      </c>
+      <c r="B25" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C25" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E25" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F25" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G25" s="3" t="str">
+        <f t="shared" si="1"/>
+        <v/>
+      </c>
+    </row>
+    <row r="26" spans="1:7" ht="15" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="10">
+        <v>2025</v>
+      </c>
+      <c r="B26" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="C26" s="26" t="s">
+        <v>147</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>9</v>
+      </c>
+      <c r="E26" s="25" t="s">
+        <v>161</v>
+      </c>
+      <c r="F26" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="G26" s="3" t="str">
         <f t="shared" si="1"/>
         <v/>
       </c>
@@ -6865,11 +7486,41 @@
   </mergeCells>
   <phoneticPr fontId="8" type="noConversion"/>
   <conditionalFormatting sqref="F3:F18">
-    <cfRule type="containsText" dxfId="5" priority="5" operator="containsText" text="*-">
+    <cfRule type="containsText" dxfId="17" priority="9" operator="containsText" text="*-">
       <formula>NOT(ISERROR(SEARCH(("*-"),(F3))))</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="F3:F18">
+    <cfRule type="colorScale" priority="10">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F19">
+    <cfRule type="containsText" dxfId="16" priority="7" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+    </cfRule>
+    <cfRule type="colorScale" priority="8">
+      <colorScale>
+        <cfvo type="formula" val="0"/>
+        <cfvo type="formula" val="1"/>
+        <cfvo type="formula" val="10"/>
+        <color rgb="FFFF9F9F"/>
+        <color rgb="FFD1E0B2"/>
+        <color rgb="FF00B050"/>
+      </colorScale>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="F20:F24">
+    <cfRule type="containsText" dxfId="15" priority="5" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+    </cfRule>
     <cfRule type="colorScale" priority="6">
       <colorScale>
         <cfvo type="formula" val="0"/>
@@ -6881,9 +7532,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F19">
-    <cfRule type="containsText" dxfId="4" priority="3" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F19))))</formula>
+  <conditionalFormatting sqref="F25">
+    <cfRule type="containsText" dxfId="1" priority="3" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F25))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="4">
       <colorScale>
@@ -6896,9 +7547,9 @@
       </colorScale>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="F20:F24">
-    <cfRule type="containsText" dxfId="3" priority="1" operator="containsText" text="*-">
-      <formula>NOT(ISERROR(SEARCH(("*-"),(F20))))</formula>
+  <conditionalFormatting sqref="F26">
+    <cfRule type="containsText" dxfId="0" priority="1" operator="containsText" text="*-">
+      <formula>NOT(ISERROR(SEARCH(("*-"),(F26))))</formula>
     </cfRule>
     <cfRule type="colorScale" priority="2">
       <colorScale>
